--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:14</t>
+    <t xml:space="preserve">2026-09-09 23:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:09</t>
+    <t xml:space="preserve">2026-09-17 14:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:05</t>
+    <t xml:space="preserve">2026-09-23 12:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:34</t>
+    <t xml:space="preserve">2026-10-02 13:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:57</t>
+    <t xml:space="preserve">2026-10-05 10:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -815,7 +815,7 @@
         <v>2020</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>156335.12</v>
+        <v>156335.13</v>
       </c>
     </row>
     <row r="17">
@@ -951,7 +951,7 @@
         <v>2020</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>136787.12</v>
+        <v>136787.13</v>
       </c>
     </row>
     <row r="25">
@@ -1087,7 +1087,7 @@
         <v>2020</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>98869.62</v>
+        <v>98869.63</v>
       </c>
     </row>
     <row r="33">
